--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dto Economico Tributario\SEGUIMIENTOS\Plan 383\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9A99C2D-64EE-47C9-960D-C11A01847A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44B943F6-8313-4EA1-8EE4-7EBBF7883CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="2775" windowWidth="21600" windowHeight="11715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="690" yWindow="3120" windowWidth="21600" windowHeight="11715" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Moratoria" sheetId="1" r:id="rId1"/>
@@ -40,22 +40,22 @@
     <t xml:space="preserve">RV     </t>
   </si>
   <si>
-    <t>Impuesto</t>
+    <t>impuesto</t>
   </si>
   <si>
-    <t>Importe_Total_Consolidado</t>
+    <t>TotConsolidado</t>
   </si>
   <si>
-    <t>Cantidad_Cuotas</t>
+    <t>ctas</t>
   </si>
   <si>
-    <t>Intereses_Resarcitorios</t>
+    <t>Resarcitorios</t>
   </si>
   <si>
-    <t>Fecha_Consolidacion</t>
+    <t>FechaConsolidacion</t>
   </si>
   <si>
-    <t>Nominal</t>
+    <t>capital</t>
   </si>
 </sst>
 </file>
@@ -399,6 +399,7 @@
   <dimension ref="A1:I3148"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
